--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/all-profiles.xlsx
@@ -1863,90 +1863,6 @@
     <t>Consent.category.text</t>
   </si>
   <si>
-    <t>Consent.category:resultType</t>
-  </si>
-  <si>
-    <t>resultType</t>
-  </si>
-  <si>
-    <t>http://fhir.de/ConsentManagement/ValueSet/ResultType</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.id</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.extension</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.id</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.extension</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.system</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.version</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.code</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.display</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Consent.category:resultType.text</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType</t>
-  </si>
-  <si>
-    <t>templateType</t>
-  </si>
-  <si>
-    <t>http://fhir.de/ConsentManagement/ValueSet/TemplateType</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.id</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.extension</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.id</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.extension</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.system</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.version</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.code</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.display</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Consent.category:templateType.text</t>
-  </si>
-  <si>
     <t>Consent.category:mii</t>
   </si>
   <si>
@@ -1992,6 +1908,90 @@
   </si>
   <si>
     <t>Consent.category:mii.text</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType</t>
+  </si>
+  <si>
+    <t>resultType</t>
+  </si>
+  <si>
+    <t>http://fhir.de/ConsentManagement/ValueSet/ResultType</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.id</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.extension</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.id</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.extension</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.system</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.version</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.code</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.display</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Consent.category:resultType.text</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType</t>
+  </si>
+  <si>
+    <t>templateType</t>
+  </si>
+  <si>
+    <t>http://fhir.de/ConsentManagement/ValueSet/TemplateType</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.id</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.extension</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.id</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.extension</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.system</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.version</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.code</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.display</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Consent.category:templateType.text</t>
   </si>
   <si>
     <t>Consent.patient</t>
@@ -17398,10 +17398,10 @@
       </c>
       <c r="F129" s="2"/>
       <c r="G129" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>85</v>
@@ -17431,7 +17431,7 @@
         <v>75</v>
       </c>
       <c r="T129" t="s" s="2">
-        <v>75</v>
+        <v>596</v>
       </c>
       <c r="U129" t="s" s="2">
         <v>75</v>
@@ -17446,11 +17446,13 @@
         <v>75</v>
       </c>
       <c r="Y129" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Z129" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="AA129" t="s" s="2">
-        <v>596</v>
+        <v>567</v>
       </c>
       <c r="AB129" t="s" s="2">
         <v>75</v>
@@ -17710,7 +17712,7 @@
         <v>84</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>85</v>
@@ -18708,7 +18710,7 @@
         <v>75</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="Z141" s="2"/>
       <c r="AA141" t="s" s="2">
@@ -19922,10 +19924,10 @@
       </c>
       <c r="F153" s="2"/>
       <c r="G153" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>85</v>
@@ -19955,7 +19957,7 @@
         <v>75</v>
       </c>
       <c r="T153" t="s" s="2">
-        <v>624</v>
+        <v>75</v>
       </c>
       <c r="U153" t="s" s="2">
         <v>75</v>
@@ -19972,11 +19974,9 @@
       <c r="Y153" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="Z153" t="s" s="2">
-        <v>566</v>
-      </c>
+      <c r="Z153" s="2"/>
       <c r="AA153" t="s" s="2">
-        <v>567</v>
+        <v>624</v>
       </c>
       <c r="AB153" t="s" s="2">
         <v>75</v>
@@ -20236,7 +20236,7 @@
         <v>84</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>85</v>
